--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488255_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488255_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7773</v>
+        <v>2.4332</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2954</v>
+        <v>2.1975</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4819</v>
+        <v>0.2357</v>
       </c>
       <c r="G2" t="n">
         <v>2.6256</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.9039</v>
+        <v>-2.248</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9886</v>
+        <v>-1.0865</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9153</v>
+        <v>-1.1615</v>
       </c>
       <c r="V2" t="n">
         <v>0.9439</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>A. GALLEGO GÓMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6914</v>
+        <v>1.5883</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4417</v>
+        <v>1.5883</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1331</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3592</v>
+        <v>1.5883</v>
       </c>
       <c r="H3" t="n">
-        <v>0.018</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3412</v>
+        <v>0.6221</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.135</v>
+        <v>1.5883</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1765</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0415</v>
+        <v>0.6221</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4942</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1944</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2997</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0977</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2873</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.385</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5034999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GALLEGO GÓMEZ</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5883</v>
+        <v>0.8637</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5883</v>
+        <v>-1.0725</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.9362</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5883</v>
+        <v>0.3592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6221</v>
+        <v>0.3412</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5883</v>
+        <v>-0.135</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.1765</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6221</v>
+        <v>0.0415</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.4942</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.1944</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.2997</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.7793</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.9255</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.3435</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.582</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.7553</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6557</v>
+        <v>-1.8527</v>
       </c>
       <c r="E5" t="n">
         <v>-0.9373</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7184</v>
+        <v>-0.9154</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0458</v>
@@ -844,13 +844,13 @@
         <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.054</v>
+        <v>-1.251</v>
       </c>
       <c r="T5" t="n">
         <v>-0.4924</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5616</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5008</v>
+        <v>-2.2004</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.746</v>
+        <v>-0.5934</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7548</v>
+        <v>-1.6071</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2563</v>
@@ -922,13 +922,13 @@
         <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3415</v>
+        <v>-1.0412</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.909</v>
+        <v>-0.7564</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4325</v>
+        <v>-0.2848</v>
       </c>
       <c r="V6" t="n">
         <v>-2.0147</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3063</v>
+        <v>-3.2521</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.335</v>
+        <v>-5.1824</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0288</v>
+        <v>1.9303</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8481</v>
@@ -1000,13 +1000,13 @@
         <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5355</v>
+        <v>-1.4814</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0732</v>
+        <v>-0.9205</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4624</v>
+        <v>-0.5609</v>
       </c>
       <c r="V7" t="n">
         <v>0.8185</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.6659</v>
+        <v>-4.0465</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.9954</v>
+        <v>-3.6469</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6704</v>
+        <v>-0.3996</v>
       </c>
       <c r="G8" t="n">
         <v>-3.6864</v>
@@ -1078,13 +1078,13 @@
         <v>2.4087</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.6323</v>
+        <v>-2.013</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0732</v>
+        <v>-0.7247</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.5592</v>
+        <v>-1.2883</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7559</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.7412</v>
+        <v>-5.1033</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.0819</v>
+        <v>-3.6901</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6593</v>
+        <v>-1.4131</v>
       </c>
       <c r="G9" t="n">
         <v>-1.789</v>
@@ -1156,13 +1156,13 @@
         <v>2.7793</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.3227</v>
+        <v>-2.6848</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5656</v>
+        <v>-1.1739</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7571</v>
+        <v>-1.5109</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6294</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1501</v>
+        <v>-7.1195</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.7701</v>
+        <v>-5.8133</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.38</v>
+        <v>-1.3062</v>
       </c>
       <c r="G10" t="n">
         <v>-2.628</v>
@@ -1234,13 +1234,13 @@
         <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6731</v>
+        <v>-1.6424</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8129</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9033</v>
+        <v>-0.8295</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4403</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.963</v>
+        <v>-18.6893</v>
       </c>
       <c r="E11" t="n">
-        <v>-17.4237</v>
+        <v>-17.1501</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.539099999999999</v>
+        <v>-1.5392</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.680499999999999</v>
+        <v>-5.6805</v>
       </c>
       <c r="H11" t="n">
         <v>5.454999999999999</v>
@@ -1285,10 +1285,10 @@
         <v>-11.1356</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1050999999999994</v>
+        <v>-0.1051000000000003</v>
       </c>
       <c r="K11" t="n">
-        <v>5.425399999999999</v>
+        <v>5.4254</v>
       </c>
       <c r="L11" t="n">
         <v>-5.5306</v>
@@ -1312,13 +1312,13 @@
         <v>16.6758</v>
       </c>
       <c r="S11" t="n">
-        <v>-13.5607</v>
+        <v>-13.2873</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.5844</v>
+        <v>-6.3108</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.9764</v>
+        <v>-6.976500000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5744</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.6918</v>
+        <v>5.0725</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5111</v>
+        <v>1.7862</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1807</v>
+        <v>3.2863</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0634</v>
+        <v>3.7333</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5579</v>
+        <v>0.5815</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5054999999999999</v>
+        <v>3.1518</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4197</v>
+        <v>3.5384</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7823</v>
+        <v>0.8629</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3626</v>
+        <v>2.6755</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3564</v>
+        <v>0.1949</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2244</v>
+        <v>-0.2814</v>
       </c>
       <c r="O12" t="n">
+        <v>0.4763</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.7411</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-2.9646</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.2234</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.4509</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.5829</v>
+      </c>
+      <c r="U12" t="n">
         <v>0.868</v>
       </c>
-      <c r="P12" t="n">
-        <v>0.3706</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-2.0382</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.4087</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5.8317</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.4444</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.3873</v>
-      </c>
       <c r="V12" t="n">
-        <v>-1.5738</v>
+        <v>0.6294</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.315</v>
+        <v>0.6294</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7944</v>
+        <v>5.0535</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8451</v>
+        <v>3.1608</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9493</v>
+        <v>1.8927</v>
       </c>
       <c r="G13" t="n">
-        <v>2.613</v>
+        <v>3.0634</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0412</v>
+        <v>2.5579</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6542</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3914</v>
+        <v>3.4197</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6099</v>
+        <v>3.7823</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0013</v>
+        <v>-0.3626</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2216</v>
+        <v>-0.3564</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5687</v>
+        <v>-1.2244</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6529</v>
+        <v>0.868</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3706</v>
+        <v>2.4087</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6817</v>
+        <v>3.1934</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3246</v>
+        <v>2.0942</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3571</v>
+        <v>1.0993</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3144</v>
+        <v>-1.5738</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.398</v>
+        <v>3.5579</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5131</v>
+        <v>1.4534</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8849</v>
+        <v>2.1045</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7333</v>
+        <v>2.613</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5815</v>
+        <v>-0.0412</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1518</v>
+        <v>2.6542</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5384</v>
+        <v>1.3914</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8629</v>
+        <v>-0.6099</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6755</v>
+        <v>2.0013</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1949</v>
+        <v>1.2216</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2814</v>
+        <v>0.5687</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4763</v>
+        <v>0.6529</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9646</v>
+        <v>-0.1853</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2234</v>
+        <v>0.3706</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2236</v>
+        <v>0.4452</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6901</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4666</v>
+        <v>0.5123</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8556</v>
+        <v>2.164</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6172</v>
+        <v>0.4361</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2384</v>
+        <v>1.7279</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4692</v>
+        <v>2.2356</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7457</v>
+        <v>-0.4062</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7235</v>
+        <v>2.6418</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.1078</v>
+        <v>2.1106</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.885</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2228</v>
+        <v>2.012</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1393</v>
+        <v>-0.5048</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4993</v>
+        <v>0.6299</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1946</v>
+        <v>1.1518</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4661</v>
+        <v>0.4754</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7285</v>
+        <v>0.6765</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5744</v>
+        <v>0.6294</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2589</v>
+        <v>0.6294</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8458</v>
+        <v>1.7538</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2921</v>
+        <v>-0.46</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5537</v>
+        <v>2.2138</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0297</v>
+        <v>-1.4692</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4814</v>
+        <v>-0.7457</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4517</v>
+        <v>-0.7235</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.7253</v>
+        <v>-2.1078</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.8083</v>
+        <v>-0.885</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0829</v>
+        <v>-1.2228</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3044</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6731</v>
+        <v>0.1393</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3687</v>
+        <v>0.4993</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5049</v>
+        <v>1.0928</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.3889</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7464</v>
+        <v>0.7038</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2589</v>
+        <v>1.5744</v>
       </c>
       <c r="W16" t="n">
         <v>1.2589</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7979</v>
+        <v>1.3052</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0675</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8653</v>
+        <v>1.209</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1112</v>
+        <v>-2.0297</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7318</v>
+        <v>-2.4814</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3794</v>
+        <v>0.4517</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3291</v>
+        <v>-1.7253</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1892</v>
+        <v>-1.8083</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1398</v>
+        <v>0.0829</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2179</v>
+        <v>-0.3044</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5426</v>
+        <v>-0.6731</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7604</v>
+        <v>0.3687</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9466</v>
+        <v>0.9644</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8556</v>
+        <v>0.5627</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0911</v>
+        <v>0.4016</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8888</v>
+        <v>1.2589</v>
       </c>
       <c r="W17" t="n">
         <v>1.2589</v>
       </c>
       <c r="X17" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7471</v>
+        <v>1.2306</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1423</v>
+        <v>-0.8092</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6048</v>
+        <v>2.0398</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2356</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4062</v>
+        <v>-0.1915</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6418</v>
+        <v>0.7957</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1106</v>
+        <v>0.2645</v>
       </c>
       <c r="K18" t="n">
         <v>0.09859999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>2.012</v>
+        <v>0.1659</v>
       </c>
       <c r="M18" t="n">
-        <v>0.125</v>
+        <v>0.3397</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5048</v>
+        <v>-0.2901</v>
       </c>
       <c r="O18" t="n">
         <v>0.6299</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.5558999999999999</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.8529</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.7793</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7349</v>
+        <v>1.4972</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1816</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5534</v>
+        <v>0.7175</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6294</v>
+        <v>-0.315</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6294</v>
+        <v>-0.0005</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0829</v>
+        <v>1.184</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8092</v>
+        <v>-1.3613</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8921</v>
+        <v>2.5453</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6042999999999999</v>
+        <v>-1.1112</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1915</v>
+        <v>-0.7318</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7957</v>
+        <v>-0.3794</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2645</v>
+        <v>-1.3291</v>
       </c>
       <c r="K19" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.1892</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1659</v>
+        <v>-1.1398</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3397</v>
+        <v>0.2179</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2901</v>
+        <v>-0.5426</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6299</v>
+        <v>0.7604</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3495</v>
+        <v>1.3328</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.5618</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5698</v>
+        <v>0.771</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.315</v>
+        <v>1.8888</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0005</v>
+        <v>1.2589</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>A. CUADRA CRESPO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.1333</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.1968</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.3301</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.3917</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3221</v>
+        <v>0.2611</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6221</v>
+        <v>0.1306</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9441000000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3221</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.2611</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.1116</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.0115</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.1231</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CUADRA CRESPO</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8309</v>
+        <v>0.9467</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2947</v>
+        <v>0.8611</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1257</v>
+        <v>0.0857</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3917</v>
+        <v>-0.4185</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2611</v>
+        <v>-1.6318</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1306</v>
+        <v>1.2133</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.3761</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.361</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.7371</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3917</v>
+        <v>-0.7945</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2611</v>
+        <v>-1.2708</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1306</v>
+        <v>0.4763</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1853</v>
+        <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1908</v>
+        <v>0.9003</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1094</v>
+        <v>0.485</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0813</v>
+        <v>0.4153</v>
       </c>
       <c r="V21" t="n">
-        <v>0.63</v>
+        <v>-1.5733</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.63</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RODRÍGUEZ LEIRO</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,28 +2125,28 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6221</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6221</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6221</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.3221</v>
       </c>
       <c r="I22" t="n">
         <v>0.6221</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6221</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.3221</v>
       </c>
       <c r="L22" t="n">
         <v>0.6221</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>A. RODRÍGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5485</v>
+        <v>0.6221</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3141</v>
+        <v>0.6221</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2344</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4185</v>
+        <v>0.6221</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6318</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2133</v>
+        <v>0.6221</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3761</v>
+        <v>0.6221</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.361</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7371</v>
+        <v>0.6221</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7945</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2708</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4763</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5949</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6901</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.09520000000000001</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8155</v>
+        <v>0.0664</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0802</v>
+        <v>-0.2968</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2647</v>
+        <v>0.3632</v>
       </c>
       <c r="G24" t="n">
         <v>0.8941</v>
@@ -2326,13 +2326,13 @@
         <v>2.0382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5879</v>
+        <v>1.4699</v>
       </c>
       <c r="T24" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.8767</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4947</v>
+        <v>0.5931</v>
       </c>
       <c r="V24" t="n">
         <v>-0.63</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2836</v>
+        <v>-5.4183</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3822</v>
+        <v>-4.6967</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9014</v>
+        <v>-0.7216</v>
       </c>
       <c r="G25" t="n">
         <v>-4.3923</v>
@@ -2404,13 +2404,13 @@
         <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2619</v>
+        <v>0.6034</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4377</v>
+        <v>0.2478</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1758</v>
+        <v>0.3556</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>18.963</v>
+        <v>19.6158</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5392</v>
+        <v>1.539199999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>17.4238</v>
+        <v>18.0767</v>
       </c>
       <c r="G26" t="n">
-        <v>5.680700000000001</v>
+        <v>5.680699999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.454999999999999</v>
+        <v>-5.455</v>
       </c>
       <c r="I26" t="n">
         <v>11.1357</v>
@@ -2458,13 +2458,13 @@
         <v>5.575299999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.02949999999999986</v>
+        <v>-0.0295000000000003</v>
       </c>
       <c r="L26" t="n">
         <v>5.604899999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1051999999999998</v>
+        <v>0.1052000000000003</v>
       </c>
       <c r="N26" t="n">
         <v>-5.4255</v>
@@ -2482,16 +2482,16 @@
         <v>14.8229</v>
       </c>
       <c r="S26" t="n">
-        <v>13.5606</v>
+        <v>14.2137</v>
       </c>
       <c r="T26" t="n">
-        <v>6.976599999999999</v>
+        <v>6.9765</v>
       </c>
       <c r="U26" t="n">
-        <v>6.5846</v>
+        <v>7.2371</v>
       </c>
       <c r="V26" t="n">
-        <v>1.574300000000001</v>
+        <v>1.5743</v>
       </c>
       <c r="W26" t="n">
         <v>5.6633</v>
